--- a/lessons/gallery/excels/remarks_required.xlsx
+++ b/lessons/gallery/excels/remarks_required.xlsx
@@ -162,7 +162,7 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-anotherDog (13:10:55.220), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -. (13:30:58.396), -log (13:30:59.108), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736), +anotherdog (00:00:00), +coneole (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00)</t>
+        <t>-anotherDog (13:10:55.220) ~0.90, -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -. (13:30:58.396), -log (13:30:59.108), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +anotherdog (00:00:00), +coneole (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H5" authorId="0" shapeId="0">
@@ -202,7 +202,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Date (13:33:53.451), -August (13:33:55.549), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+        <t>-console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -227,7 +227,7 @@
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +, (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +, (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -247,7 +247,7 @@
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -Thursday (13:36:45.577), -Friday (13:36:53.097), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +Wednesday (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00)</t>
+        <t>-myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +Wednesday (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -267,7 +267,7 @@
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-+ (13:19:45.738), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713), -, (13:29:49.778), -s3 (13:29:51.023), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
+        <t>-+ (13:19:45.738) ~0.00, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713) ~0.00, -, (13:29:49.778), -s3 (13:29:51.023), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
@@ -287,7 +287,7 @@
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-dog (13:05:03.658), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -dog (13:07:52.399), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -console (13:34:01.942), +Dog (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +" (00:00:00), +" (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +cosole (00:00:00)</t>
+        <t>-dog (13:05:03.658) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -dog (13:07:52.399) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -console (13:34:01.942) ~0.86, +Dog (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +" (00:00:00), +" (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +cosole (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -307,7 +307,7 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+        <t>-` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -337,7 +337,7 @@
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, anpotherDog, defeault, html, powb, someData, underdefined, log*</t>
+        <t xml:space="preserve"> , " (x2), ' (x2), , (x3), -, /, anpotherDog, defeault, html, powb, someData, underdefined, log*</t>
       </text>
     </comment>
     <comment ref="H36" authorId="0" shapeId="0">
@@ -347,17 +347,17 @@
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
-        <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +anpotherDog (00:00:00), +defeault (00:00:00), +html (00:00:00), +powb (00:00:00), +someData (00:00:00), +underdefined (00:00:00), -! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -https (13:09:28.845), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967), -break (13:38:10.544), -; (13:38:10.869)</t>
+        <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +anpotherDog (00:00:00), +defeault (00:00:00), +html (00:00:00), +powb (00:00:00), +someData (00:00:00), +underdefined (00:00:00), -! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -https (13:09:28.845), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967)</t>
       </text>
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -https (13:09:28.845), +- (00:00:00), +html (00:00:00)</t>
+        <t>-! (12:24:11.928), -= (12:24:13.188) ~0.00, -/ (12:29:39.313), -https (13:09:28.845) ~0.40, +- (00:00:00), +html (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967), -break (13:38:10.544), -; (13:38:10.869), +underdefined (00:00:00), +, (00:00:00), +, (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +  (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +defeault (00:00:00), +/ (00:00:00)</t>
+        <t>-undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027) ~0.00, -anotherDog (13:10:55.220) ~0.91, -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -default (13:37:00.967) ~0.88, +underdefined (00:00:00), +, (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +  (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +defeault (00:00:00), +/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E41" authorId="0" shapeId="0">
@@ -377,12 +377,12 @@
     </comment>
     <comment ref="M41" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +, (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00)</t>
+        <t>-&lt; (12:27:55.192), -/ (12:27:55.202) ~0.00, -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +, (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O41" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -402,12 +402,12 @@
     </comment>
     <comment ref="M42" authorId="0" shapeId="0">
       <text>
-        <t>-Emmet (12:28:58.636), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +Emnet (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+        <t>-Emmet (12:28:58.636) ~0.80, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +Emnet (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -switch (13:35:50.520), +anotherdog (00:00:00), +anotherdog (00:00:00), +swtich (00:00:00)</t>
+        <t>-anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -switch (13:35:50.520) ~0.67, +anotherdog (00:00:00), +anotherdog (00:00:00), +swtich (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E45" authorId="0" shapeId="0">
@@ -427,12 +427,12 @@
     </comment>
     <comment ref="M45" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -getDay (13:34:50.180), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +getDate (00:00:00)</t>
+        <t>-' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -getDay (13:34:50.180) ~0.71, +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +getDate (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -452,7 +452,7 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -default (13:37:00.967), +defult (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -default (13:37:00.967) ~0.86, +defult (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -472,12 +472,12 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), -initial (12:24:13.118), -/ (12:29:39.313), +Viewport (00:00:00), +intial (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -/ (12:29:39.313), +Viewport (00:00:00), +intial (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+        <t>-console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -497,12 +497,12 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -527,7 +527,7 @@
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
       <text>
-        <t>", ' (x2), , (x2), a</t>
+        <t>", ' (x2), ,, a</t>
       </text>
     </comment>
     <comment ref="H56" authorId="0" shapeId="0">
@@ -537,12 +537,12 @@
     </comment>
     <comment ref="J56" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +a (00:00:00), -" (13:29:31.463)</t>
+        <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +a (00:00:00), -" (13:29:31.463)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-" (13:29:31.463), +, (00:00:00), +a (00:00:00), +, (00:00:00), +' (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+        <t>-" (13:29:31.463) ~0.00, +a (00:00:00), +, (00:00:00), +' (00:00:00), +" (00:00:00), +' (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -562,7 +562,7 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+        <t>-= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D61" authorId="0" shapeId="0">
@@ -592,12 +592,12 @@
     </comment>
     <comment ref="O61" authorId="0" shapeId="0">
       <text>
-        <t>-console (12:33:56.141), -const (12:35:25.644), -myString (12:35:27.676), -! (12:42:04.755), -console (12:43:10.202), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -' (13:28:30.981), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +consloe (00:00:00), +connstmyString (00:00:00), +Console (00:00:00), +appendchild (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+        <t>-console (12:33:56.141) ~0.71, -const (12:35:25.644), -myString (12:35:27.676), -! (12:42:04.755), -console (12:43:10.202) ~0.86, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +consloe (00:00:00), +connstmyString (00:00:00), +Console (00:00:00), +appendchild (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -617,7 +617,7 @@
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-brown (13:05:24.043), +brows (00:00:00)</t>
+        <t>-brown (13:05:24.043) ~0.80, +brows (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -637,12 +637,12 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+        <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
       <text>
-        <t>" (x3), ,, /, 1 (x2), &lt;, &gt; (x2), agust, breake (x3), getDate, gog, javascriptlesson, muBoolean, title, log*</t>
+        <t>" (x2), ,, /, 1 (x2), &lt;, &gt; (x2), agust, breake (x3), getDate, gog, javascriptlesson, muBoolean, title, log*</t>
       </text>
     </comment>
     <comment ref="H68" authorId="0" shapeId="0">
@@ -652,22 +652,22 @@
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +getDate (00:00:00), +gog (00:00:00), +javascriptlesson (00:00:00), +muBoolean (00:00:00), +title (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+        <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +getDate (00:00:00), +gog (00:00:00), +javascriptlesson (00:00:00), +muBoolean (00:00:00), +title (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
       </text>
     </comment>
     <comment ref="M68" authorId="0" shapeId="0">
       <text>
-        <t>-  (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +" (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +&gt; (00:00:00)</t>
+        <t>-  (00:00:00) ~0.00, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736), +muBoolean (00:00:00), +gog (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00)</t>
+        <t>-myBoolean (12:38:28.108) ~0.89, +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114) ~0.67, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +muBoolean (00:00:00), +gog (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
       <text>
-        <t>", , (x2), / (x3), Console, aage, anoherDog, muBoolean, muNumber, } (x5), ´ (x2)</t>
+        <t>, (x2), / (x3), Console, aage, anoherDog, muBoolean, muNumber, } (x5), ´ (x2)</t>
       </text>
     </comment>
     <comment ref="H70" authorId="0" shapeId="0">
@@ -677,17 +677,17 @@
     </comment>
     <comment ref="J70" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +Console (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -; (13:02:35.373), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376)</t>
+        <t>+, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +Console (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-! (12:30:40.873), +" (00:00:00), +/ (00:00:00)</t>
+        <t>+/ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -; (13:02:35.373), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376), +muNumber (00:00:00), +muBoolean (00:00:00), +, (00:00:00), +, (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -. (12:58:07.899) ~0.00, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -` (13:32:14.220) ~0.00, -console (13:34:46.231) ~0.86, -} (13:35:58.376), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +, (00:00:00), +, (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H71" authorId="0" shapeId="0">
@@ -722,12 +722,12 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+        <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +todat (00:00:00)</t>
+        <t>-console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +todat (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H73" authorId="0" shapeId="0">
@@ -747,7 +747,7 @@
     </comment>
     <comment ref="J75" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +browen (00:00:00), +charlie (00:00:00), +getday (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +today (00:00:00), +underfined (00:00:00), +view (00:00:00), -viewport (12:24:12.738), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+        <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +browen (00:00:00), +charlie (00:00:00), +getday (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +today (00:00:00), +underfined (00:00:00), +view (00:00:00), -viewport (12:24:12.738), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
       </text>
     </comment>
     <comment ref="M75" authorId="0" shapeId="0">
@@ -757,27 +757,27 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +today (00:00:00), +getday (00:00:00)</t>
+        <t>-myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -\ (13:29:38.349) ~0.00, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +today (00:00:00), +getday (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve"> , " (x2), ,, lig, oppositeBolean, log*</t>
+        <t xml:space="preserve"> , ,, lig, oppositeBolean, log*</t>
       </text>
     </comment>
     <comment ref="J78" authorId="0" shapeId="0">
       <text>
-        <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +, (00:00:00), +lig (00:00:00), +oppositeBolean (00:00:00), -log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969)</t>
+        <t>+  (00:00:00), +, (00:00:00), +lig (00:00:00), +oppositeBolean (00:00:00), -log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969)</t>
       </text>
     </comment>
     <comment ref="M78" authorId="0" shapeId="0">
       <text>
-        <t>+" (00:00:00), +" (00:00:00), +  (00:00:00)</t>
+        <t>+  (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +, (00:00:00)</t>
+        <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +, (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E79" authorId="0" shapeId="0">
@@ -797,12 +797,12 @@
     </comment>
     <comment ref="M79" authorId="0" shapeId="0">
       <text>
-        <t>-ol (12:30:53.144), +old (00:00:00)</t>
+        <t>-ol (12:30:53.144) ~0.67, +old (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-% (13:22:03.842), +&amp; (00:00:00)</t>
+        <t>-% (13:22:03.842) ~0.00, +&amp; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="H81" authorId="0" shapeId="0">
@@ -842,7 +842,7 @@
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>+log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), +somedate (00:00:00)</t>
+        <t>+log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, +somedate (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-anotherDog (13:10:55.220), -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -. (13:30:58.396), -log (13:30:59.108), -` (13:31:57.168), -` (13:32:14.220), -August (13:33:55.549), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736), +anotherdog (00:00:00), +coneole (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00)</t>
+          <t>-anotherDog (13:10:55.220) ~0.90, -console (13:21:51.707), -. (13:21:51.847), -log (13:21:52.467), -( (13:21:52.626), -a (13:21:52.848), -* (13:21:53.321), -b (13:21:53.875), -) (13:21:54.226), -; (13:21:54.515), -a (13:22:44.245), -, (13:22:44.802), -console (13:26:17.050) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -. (13:30:58.396), -log (13:30:59.108), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -August (13:33:55.549) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:22.736) ~0.83, +anotherdog (00:00:00), +coneole (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +} (00:00:00), +" (00:00:00), +Agust (00:00:00), +braeak (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Date (13:33:53.451), -August (13:33:55.549), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
+          <t>-console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +  (00:00:00), +" (00:00:00), +date (00:00:00), +Agust (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -. (13:19:44.184), -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168), -` (13:32:14.220), -Weekend (13:37:10.693), +, (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -. (13:19:44.184) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -, (13:29:49.778), -s3 (13:29:51.023), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -Weekend (13:37:10.693) ~0.00, +, (00:00:00), +' (00:00:00), +' (00:00:00), +Monday (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178), -" (13:28:16.692), -" (13:29:13.699), -" (13:29:31.463), -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -Thursday (13:36:45.577), -Friday (13:36:53.097), +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +Wednesday (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00)</t>
+          <t>-myBoolean (12:41:00.416), -= (12:41:00.970), -false (12:41:02.595), -; (12:41:04.494), -console (13:23:33.257), -. (13:23:33.449), -log (13:23:34.111), -( (13:23:34.331), -b (13:23:34.620), -* (13:23:35.254), -* (13:23:35.578), -0 (13:23:37.240), -. (13:23:37.501), -5 (13:23:37.769), -) (13:23:38.049), -; (13:23:38.474), -" (13:28:12.178) ~0.00, -" (13:28:16.692) ~0.00, -" (13:29:13.699), -" (13:29:31.463) ~0.00, -\ (13:29:35.759), -\ (13:29:38.349), -" (13:29:40.572) ~0.00, -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -Thursday (13:36:45.577) ~0.44, -Friday (13:36:53.097) ~0.50, +' (00:00:00), +' (00:00:00), +` (00:00:00), +` (00:00:00), +Wednesday (00:00:00), +Thursday (00:00:00), +case (00:00:00), +6 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Friday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00), +case (00:00:00), +7 (00:00:00), +: (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +" (00:00:00), +It (00:00:00), +' (00:00:00), +s (00:00:00), +Saturday (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +break (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-+ (13:19:45.738), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713), -, (13:29:49.778), -s3 (13:29:51.023), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
+          <t>-+ (13:19:45.738) ~0.00, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:38.713) ~0.00, -, (13:29:49.778), -s3 (13:29:51.023), +* (00:00:00), +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-dog (13:05:03.658), -dog (13:05:41.351), -dog (13:06:11.686), -dog (13:07:08.730), -dog (13:07:35.114), -dog (13:07:52.399), -container (13:13:27.309), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -* (13:25:54.969), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -console (13:34:01.942), +Dog (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +" (00:00:00), +" (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +cosole (00:00:00)</t>
+          <t>-dog (13:05:03.658) ~0.67, -dog (13:05:41.351) ~0.67, -dog (13:06:11.686) ~0.67, -dog (13:07:08.730) ~0.67, -dog (13:07:35.114) ~0.67, -dog (13:07:52.399) ~0.67, -container (13:13:27.309) ~0.89, -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -* (13:25:54.969) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -console (13:34:01.942) ~0.86, +Dog (00:00:00), +, (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Dog (00:00:00), +Container (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), ++ (00:00:00), +" (00:00:00), +" (00:00:00), +i (00:00:00), +' (00:00:00), +i (00:00:00), +' (00:00:00), +cosole (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-` (13:31:57.168), -` (13:32:14.220), +' (00:00:00), +' (00:00:00)</t>
+          <t>-` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, +' (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2767,11 +2767,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> , " (x2), ' (x2), , (x4), -, /, anpotherDog, defeault, html, powb, someData, underdefined, log*</t>
+          <t xml:space="preserve"> , " (x2), ' (x2), , (x3), -, /, anpotherDog, defeault, html, powb, someData, underdefined, log*</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2786,11 +2786,11 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>96.59999999999999</v>
+        <v>97</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +anpotherDog (00:00:00), +defeault (00:00:00), +html (00:00:00), +powb (00:00:00), +someData (00:00:00), +underdefined (00:00:00), -! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -https (13:09:28.845), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967), -break (13:38:10.544), -; (13:38:10.869)</t>
+          <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +, (00:00:00), +- (00:00:00), +/ (00:00:00), +anpotherDog (00:00:00), +defeault (00:00:00), +html (00:00:00), +powb (00:00:00), +someData (00:00:00), +underdefined (00:00:00), -! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -https (13:09:28.845), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2799,15 +2799,15 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-! (12:24:11.928), -= (12:24:13.188), -/ (12:29:39.313), -https (13:09:28.845), +- (00:00:00), +html (00:00:00)</t>
+          <t>-! (12:24:11.928), -= (12:24:13.188) ~0.00, -/ (12:29:39.313), -https (13:09:28.845) ~0.40, +- (00:00:00), +html (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
-        <v>96.3</v>
+        <v>96.8</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-undefined (12:43:17.799), -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027), -anotherDog (13:10:55.220), -pow (13:23:18.094), -. (13:23:20.954), -. (13:23:37.501), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:33:51.019), -default (13:37:00.967), -break (13:38:10.544), -; (13:38:10.869), +underdefined (00:00:00), +, (00:00:00), +, (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +  (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +defeault (00:00:00), +/ (00:00:00)</t>
+          <t>-undefined (12:43:17.799) ~0.75, -myArray (12:48:11.391), -. (12:48:11.846), -length (12:48:14.079), -= (12:48:17.153), -0 (12:48:17.851), -; (12:48:18.482), +log* (12:53:22.757), -error (12:53:23.899), -. (13:07:09.027) ~0.00, -anotherDog (13:10:55.220) ~0.91, -pow (13:23:18.094) ~0.75, -. (13:23:20.954) ~0.00, -. (13:23:37.501) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:33:51.019) ~0.88, -default (13:37:00.967) ~0.88, +underdefined (00:00:00), +, (00:00:00), +anpotherDog (00:00:00), +powb (00:00:00), +, (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +  (00:00:00), +' (00:00:00), +' (00:00:00), +someData (00:00:00), +defeault (00:00:00), +/ (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-&lt; (12:27:55.192), -/ (12:27:55.202), -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +, (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00)</t>
+          <t>-&lt; (12:27:55.192), -/ (12:27:55.202) ~0.00, -&lt; (12:29:39.103), -li (12:29:39.123), -&gt; (12:29:39.133), -&lt; (12:29:39.143), -/ (12:29:39.153), -li (12:29:39.173), -&gt; (12:29:39.183), -&lt; (12:29:39.203), -li (12:29:39.223), -&gt; (12:29:39.233), -&lt; (12:29:39.243), -/ (12:29:39.253), -li (12:29:39.273), -&gt; (12:29:39.283), -/ (12:29:39.313), -div (12:30:47.087), -# (12:30:47.193), -container (12:30:48.969), -( (12:30:49.458), -div (12:30:50.033), -with (12:30:50.841), -id (12:30:51.528), -) (12:30:51.709), -ol (12:30:53.144), -&gt; (12:30:53.364), -li (12:30:54.573), -* (12:30:55.091), -3 (12:30:55.908), -( (12:31:00.957), -ordered (12:31:02.226), -list (12:31:03.447), -with (12:31:04.534), -3 (12:31:04.810), -items (12:31:06.206), -) (12:31:06.395), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:16.821), -script (13:09:18.025), -src (13:09:19.805), -= (13:09:20.427), -" (13:09:20.914), -" (13:09:20.924), -https (13:09:28.845), -: (13:09:28.963), -/ (13:09:31.443), -/ (13:09:31.994), -www (13:09:33.787), -. (13:09:34.163), -radufromfinland (13:09:39.343), -. (13:09:39.613), -com (13:09:41.214), -/ (13:09:41.395), -dog (13:09:43.134), -. (13:09:43.462), -js (13:09:44.449), -&gt; (13:09:45.189), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +' (00:00:00), +; (00:00:00), +cript (00:00:00), +&gt; (00:00:00), +mynumber (00:00:00), +123456 (00:00:00), +mystring (00:00:00), +my (00:00:00), +string (00:00:00), +opposite (00:00:00), +Boolean (00:00:00), +MyBoolean (00:00:00), +oppositeboolean (00:00:00), +, (00:00:00), +appendchild (00:00:00), +no (00:00:00), +need (00:00:00), +for (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +container (00:00:00), +" (00:00:00), +) (00:00:00), +ids (00:00:00), +that (00:00:00), +are (00:00:00), +valid (00:00:00), +JS (00:00:00), +names (00:00:00), +are (00:00:00), +automatically (00:00:00), +global (00:00:00), +variables (00:00:00), +invalid (00:00:00), +names (00:00:00), +: (00:00:00), +* (00:00:00), +start (00:00:00), +with (00:00:00), +a (00:00:00), +numbers (00:00:00), +* (00:00:00), +contain (00:00:00), +spaces (00:00:00), +or (00:00:00), +special (00:00:00), +characters (00:00:00), +( (00:00:00), +like (00:00:00), +- (00:00:00), +) (00:00:00), +* (00:00:00), +/ (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myNumber (12:33:59.949), -myString (12:35:27.676), -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416), -oppositeBoolean (12:41:07.806), -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342), -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myNumber (12:33:59.949) ~0.00, -myString (12:35:27.676) ~0.88, -myString (12:35:43.276), -= (12:36:44.740), -! (12:36:45.837), -myBoolean (12:36:56.090), -oppositeBoolean (12:38:31.842), -myBoolean (12:41:00.416) ~0.89, -oppositeBoolean (12:41:07.806) ~0.93, -; (12:48:50.236), -; (12:48:53.831), -function (13:02:27.510), -( (13:02:27.770), -a (13:02:28.064), -, (13:02:28.451), -b (13:02:29.161), -) (13:02:29.546), -{ (13:02:29.863), -return (13:02:31.777), -a (13:02:32.226), -- (13:02:34.319), -b (13:02:34.848), -; (13:02:35.373), -} (13:02:46.659), -appendChild (13:13:30.342) ~0.91, -console (13:22:11.787), -. (13:22:11.931), -log (13:22:12.594), -( (13:22:12.841), -a (13:22:13.092), -* (13:22:13.572), -* (13:22:13.913), -b (13:22:15.299), -) (13:22:15.560), -; (13:22:16.047), -const (13:28:09.997), -s1 (13:28:10.602), -= (13:28:11.050), -" (13:28:12.178), -Welcome (13:28:13.560), -to (13:28:14.166), -Karelia (13:28:16.030), -! (13:28:16.362), -" (13:28:16.692), -; (13:28:17.854), -const (13:28:24.699), -s2 (13:28:25.337), -= (13:28:25.791), -' (13:28:26.250), -Welcome (13:28:27.998), -to (13:28:28.668), -Karelia (13:28:30.418), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -console (13:28:34.097), -. (13:28:34.373), -log (13:28:35.076), -( (13:28:35.248), -s1 (13:28:35.746), -, (13:28:35.960), -s2 (13:28:36.977), -) (13:28:37.211), -; (13:28:37.833), -" (13:29:13.699), -" (13:29:15.871), -const (13:29:29.792), -s3 (13:29:30.471), -= (13:29:30.929), -" (13:29:31.463), -Welcome (13:29:34.675), -to (13:29:35.300), -\ (13:29:35.759), -" (13:29:36.010), -Karelia (13:29:38.066), -\ (13:29:38.349), -" (13:29:38.713), -! (13:29:39.865), -" (13:29:40.572), -; (13:29:40.974), -, (13:29:49.778), -s3 (13:29:51.023), -const (13:30:47.762), -age (13:30:48.674), -= (13:30:49.425), -36 (13:30:50.077), -; (13:30:50.815), -console (13:30:58.191), -. (13:30:58.396), -log (13:30:59.108), -( (13:30:59.326), -" (13:30:59.521), -I (13:30:59.741), -am (13:31:00.525), -" (13:31:00.978), -+ (13:31:02.188), -age (13:31:03.542), -+ (13:31:03.925), -" (13:31:04.406), -years (13:31:05.818), -old (13:31:06.881), -" (13:31:07.110), -) (13:31:07.394), -; (13:31:07.806), -console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -let (13:33:48.993), -someDate (13:33:51.019), -= (13:33:51.416), -new (13:33:52.269), -Date (13:33:53.451), -( (13:33:53.750), -" (13:33:53.872), -August (13:33:55.549), -24 (13:33:56.247), -, (13:33:56.552), -2025 (13:33:58.460), -" (13:33:59.175), -) (13:33:59.683), -; (13:34:00.044), -console (13:34:01.942), -. (13:34:02.169), -log (13:34:02.768), -( (13:34:02.996), -someDate (13:34:04.667), -) (13:34:04.969), -; (13:34:05.226), -console (13:34:46.231), -. (13:34:46.485), -log (13:34:47.116), -( (13:34:47.310), -today (13:34:48.450), -. (13:34:48.684), -getDay (13:34:50.180), -( (13:34:50.372), -) (13:34:50.567), -) (13:34:51.041), -; (13:34:51.441), -switch (13:35:50.520), -( (13:35:51.352), -today (13:35:52.680), -. (13:35:52.915), -getDay (13:35:54.315), -( (13:35:54.689), -) (13:35:55.540), -) (13:35:56.015), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-Emmet (12:28:58.636), -ol (12:29:38.973), -/ (12:29:39.313), -ol (12:29:39.333), -ol (12:30:53.144), +Emnet (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
+          <t>-Emmet (12:28:58.636) ~0.80, -ol (12:29:38.973) ~0.50, -/ (12:29:39.313), -ol (12:29:39.333) ~0.50, -ol (12:30:53.144) ~0.50, +Emnet (00:00:00), +o1 (00:00:00), +o1 (00:00:00), +o1 (00:00:00)</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-anotherDog (13:11:21.260), -anotherDog (13:13:17.733), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -switch (13:35:50.520), +anotherdog (00:00:00), +anotherdog (00:00:00), +swtich (00:00:00)</t>
+          <t>-anotherDog (13:11:21.260) ~0.90, -anotherDog (13:13:17.733) ~0.90, -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -switch (13:35:50.520) ~0.67, +anotherdog (00:00:00), +anotherdog (00:00:00), +swtich (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168), -` (13:32:14.220), -getDay (13:34:50.180), +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +getDate (00:00:00)</t>
+          <t>-' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -getDay (13:34:50.180) ~0.71, +" (00:00:00), +" (00:00:00), +' (00:00:00), +' (00:00:00), +getDate (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -default (13:37:00.967), +defult (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -console (13:22:01.859), -. (13:22:02.110), -log (13:22:02.836), -( (13:22:03.038), -a (13:22:03.297), -% (13:22:03.842), -b (13:22:04.523), -) (13:22:05.089), -; (13:22:05.323), -a (13:25:59.379), -/ (13:26:00.029), -= (13:26:00.357), -3 (13:26:01.048), -; (13:26:02.451), -default (13:37:00.967) ~0.86, +defult (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), -initial (12:24:13.118), -/ (12:29:39.313), +Viewport (00:00:00), +intial (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.88, -initial (12:24:13.118) ~0.86, -/ (12:29:39.313), +Viewport (00:00:00), +intial (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -console (13:31:42.392), -Date (13:33:24.732), -Date (13:33:53.451), -August (13:33:55.549), -console (13:37:07.678), +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
+          <t>-console (13:21:56.654), -. (13:21:56.770), -log (13:21:57.463), -( (13:21:57.719), -a (13:21:57.948), -/ (13:21:58.455), -b (13:21:59.074), -) (13:21:59.346), -; (13:21:59.792), -Number (13:24:27.105) ~0.86, -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -console (13:31:42.392) ~0.86, -Date (13:33:24.732) ~0.75, -Date (13:33:53.451) ~0.75, -August (13:33:55.549) ~0.83, -console (13:37:07.678) ~0.86, +Numbers (00:00:00), +" (00:00:00), +" (00:00:00), +cosole (00:00:00), +date (00:00:00), +date (00:00:00), +Agust (00:00:00), +comsole (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053), -default (13:37:00.967), +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -, (13:05:10.053) ~0.00, -default (13:37:00.967) ~0.14, +myArray (00:00:00), += (00:00:00), +[ (00:00:00), +1 (00:00:00), +, (00:00:00), +2 (00:00:00), +, (00:00:00), +3 (00:00:00), +] (00:00:00), +; (00:00:00), +; (00:00:00), +% (00:00:00), +case (00:00:00), +5 (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>", ' (x2), , (x2), a</t>
+          <t>", ' (x2), ,, a</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -3768,11 +3768,11 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +, (00:00:00), +a (00:00:00), -" (13:29:31.463)</t>
+          <t>+" (00:00:00), +' (00:00:00), +' (00:00:00), +, (00:00:00), +a (00:00:00), -" (13:29:31.463)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3781,11 +3781,11 @@
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-" (13:29:31.463), +, (00:00:00), +a (00:00:00), +, (00:00:00), +' (00:00:00), +" (00:00:00), +' (00:00:00)</t>
+          <t>-" (13:29:31.463) ~0.00, +a (00:00:00), +, (00:00:00), +' (00:00:00), +" (00:00:00), +' (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168), -` (13:32:14.220), -someDate (13:34:04.667), -console (13:34:46.231), -today (13:35:52.680), -2 (13:36:26.214), -3 (13:36:33.970), -4 (13:36:41.079), -5 (13:36:48.097), +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
+          <t>-= (13:26:10.651), -' (13:28:26.250), -' (13:28:30.981), -` (13:31:57.168) ~0.00, -` (13:32:14.220) ~0.00, -someDate (13:34:04.667) ~0.88, -console (13:34:46.231) ~0.86, -today (13:35:52.680) ~0.60, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -4 (13:36:41.079) ~0.00, -5 (13:36:48.097) ~0.00, +" (00:00:00), +" (00:00:00), +SomeDate (00:00:00), +Console (00:00:00), +toady (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00), +1 (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>-console (12:33:56.141), -const (12:35:25.644), -myString (12:35:27.676), -! (12:42:04.755), -console (12:43:10.202), -appendChild (13:13:30.342), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250), -' (13:28:30.981), -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +consloe (00:00:00), +connstmyString (00:00:00), +Console (00:00:00), +appendchild (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00)</t>
+          <t>-console (12:33:56.141) ~0.71, -const (12:35:25.644), -myString (12:35:27.676), -! (12:42:04.755), -console (12:43:10.202) ~0.86, -appendChild (13:13:30.342) ~0.91, -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -console (13:20:14.805), -. (13:20:14.947), -log (13:20:15.669), -( (13:20:15.840), -a (13:20:16.103), -+ (13:20:16.526), -b (13:20:16.935), -) (13:20:17.157), -; (13:20:17.407), -' (13:28:26.250) ~0.00, -' (13:28:30.981) ~0.00, -{ (13:35:57.002), -} (13:35:58.376), -case (13:36:12.690), -1 (13:36:13.308), -: (13:36:13.587), -console (13:36:15.617), -. (13:36:15.769), -log (13:36:16.407), -( (13:36:16.640), -" (13:36:16.932), -Monday (13:36:18.214), -" (13:36:18.430), -) (13:36:18.700), -; (13:36:19.272), -case (13:36:25.840), -2 (13:36:26.214), -: (13:36:26.457), -console (13:36:28.233), -. (13:36:28.484), -log (13:36:29.389), -( (13:36:29.564), -" (13:36:29.820), -Tuesday (13:36:31.309), -" (13:36:31.623), -) (13:36:31.694), -; (13:36:32.278), -case (13:36:33.386), -3 (13:36:33.970), -: (13:36:34.083), -console (13:36:35.797), -. (13:36:36.002), -log (13:36:36.572), -( (13:36:36.825), -" (13:36:37.020), -Wednesday (13:36:38.686), -" (13:36:38.926), -) (13:36:39.166), -; (13:36:39.359), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +consloe (00:00:00), +connstmyString (00:00:00), +Console (00:00:00), +appendchild (00:00:00), +" (00:00:00), +" (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-brown (13:05:24.043), +brows (00:00:00)</t>
+          <t>-brown (13:05:24.043) ~0.80, +brows (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-oppositeBoolean (12:41:07.806), -oppositeBoolean (12:41:21.351), +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029), -log (13:19:44.775), -' (13:28:26.250), -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
+          <t>-oppositeBoolean (12:41:07.806) ~0.93, -oppositeBoolean (12:41:21.351) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -console (13:19:44.029) ~0.00, -log (13:19:44.775) ~0.00, -' (13:28:26.250) ~0.00, -' (13:28:30.981), -" (13:29:13.699), +oppositrBoolean (00:00:00), +oppositrBoolean (00:00:00), +CONSOLE (00:00:00), +LOG (00:00:00), +Math (00:00:00), +. (00:00:00), +pow (00:00:00), +( (00:00:00), +) (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>" (x3), ,, /, 1 (x2), &lt;, &gt; (x2), agust, breake (x3), getDate, gog, javascriptlesson, muBoolean, title, log*</t>
+          <t>" (x2), ,, /, 1 (x2), &lt;, &gt; (x2), agust, breake (x3), getDate, gog, javascriptlesson, muBoolean, title, log*</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -4354,20 +4354,20 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +getDate (00:00:00), +gog (00:00:00), +javascriptlesson (00:00:00), +muBoolean (00:00:00), +title (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
+          <t>+" (00:00:00), +" (00:00:00), +, (00:00:00), +/ (00:00:00), +1 (00:00:00), +1 (00:00:00), +&lt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +agust (00:00:00), +breake (00:00:00), +breake (00:00:00), +breake (00:00:00), +getDate (00:00:00), +gog (00:00:00), +javascriptlesson (00:00:00), +muBoolean (00:00:00), +title (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>92.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-  (00:00:00), -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +" (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +&gt; (00:00:00)</t>
+          <t>-  (00:00:00) ~0.00, -&lt; (12:32:51.935), -script (12:32:51.995), -&gt; (12:32:52.005), -&lt; (13:09:45.302), -/ (13:09:45.312), -script (13:09:45.372), -&gt; (13:09:45.382), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00), +javascriptlesson (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-myBoolean (12:38:28.108), +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114), -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501), -! (13:28:16.362), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549), -getDay (13:35:54.315), -2 (13:36:26.214), -3 (13:36:33.970), -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -break (13:38:20.154), -break (13:38:22.736), +muBoolean (00:00:00), +gog (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00)</t>
+          <t>-myBoolean (12:38:28.108) ~0.89, +log* (12:53:22.757), -error (12:53:23.899), -dog (13:07:35.114) ~0.67, -" (13:20:07.578), -" (13:20:08.157), -. (13:23:37.501) ~0.00, -! (13:28:16.362), -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981) ~0.00, -" (13:29:13.699), -" (13:29:15.871), -" (13:29:36.010), -August (13:33:55.549) ~0.67, -getDay (13:35:54.315) ~0.71, -2 (13:36:26.214) ~0.00, -3 (13:36:33.970) ~0.00, -case (13:36:40.739), -4 (13:36:41.079), -: (13:36:41.316), -console (13:36:42.921), -. (13:36:43.032), -log (13:36:43.702), -( (13:36:43.826), -" (13:36:44.047), -Thursday (13:36:45.577), -" (13:36:45.733), -) (13:36:45.933), -; (13:36:46.343), -case (13:36:47.675), -5 (13:36:48.097), -: (13:36:48.333), -console (13:36:50.123), -. (13:36:50.344), -log (13:36:50.999), -( (13:36:51.100), -" (13:36:51.740), -Friday (13:36:53.097), -" (13:36:53.328), -) (13:36:53.603), -; (13:36:54.006), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679) ~0.83, -break (13:38:20.154) ~0.83, -break (13:38:22.736) ~0.83, +muBoolean (00:00:00), +gog (00:00:00), +, (00:00:00), +" (00:00:00), +" (00:00:00), +agust (00:00:00), +getDate (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00), +1 (00:00:00), +breake (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4441,11 +4441,11 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>", , (x2), / (x3), Console, aage, anoherDog, muBoolean, muNumber, } (x5), ´ (x2)</t>
+          <t>, (x2), / (x3), Console, aage, anoherDog, muBoolean, muNumber, } (x5), ´ (x2)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -4460,28 +4460,28 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +Console (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -! (12:30:40.873), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -; (13:02:35.373), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376)</t>
+          <t>+, (00:00:00), +, (00:00:00), +/ (00:00:00), +/ (00:00:00), +/ (00:00:00), +Console (00:00:00), +aage (00:00:00), +anoherDog (00:00:00), +muBoolean (00:00:00), +muNumber (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +´ (00:00:00), +´ (00:00:00), -myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-! (12:30:40.873), +" (00:00:00), +/ (00:00:00)</t>
+          <t>+/ (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-myNumber (12:33:44.402), -myBoolean (12:36:27.967), -. (12:58:07.899), -; (13:02:35.373), -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260), -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759), -" (13:29:36.010), -\ (13:29:38.349), -age (13:30:48.674), -` (13:32:14.220), -console (13:34:46.231), -} (13:35:58.376), +muNumber (00:00:00), +muBoolean (00:00:00), +, (00:00:00), +, (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+          <t>-myNumber (12:33:44.402) ~0.88, -myBoolean (12:36:27.967) ~0.89, -. (12:58:07.899) ~0.00, -, (13:05:10.053), -, (13:05:21.265), -anotherDog (13:11:21.260) ~0.90, -" (13:29:13.699), -" (13:29:15.871), -\ (13:29:35.759) ~0.00, -" (13:29:36.010), -\ (13:29:38.349) ~0.00, -age (13:30:48.674) ~0.75, -` (13:32:14.220) ~0.00, -console (13:34:46.231) ~0.86, -} (13:35:58.376), -; (13:38:10.869), +muNumber (00:00:00), +muBoolean (00:00:00), +, (00:00:00), +, (00:00:00), +anoherDog (00:00:00), +/ (00:00:00), +´ (00:00:00), +/ (00:00:00), +aage (00:00:00), +´ (00:00:00), +Console (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-viewport (12:24:12.738), +viewpoint (00:00:00)</t>
+          <t>-viewport (12:24:12.738) ~0.78, +viewpoint (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697), -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +todat (00:00:00)</t>
+          <t>-console (13:31:42.392), -. (13:31:42.523), -log (13:31:43.526), -( (13:31:43.816), -` (13:31:57.168), -I (13:32:08.777), -am (13:32:09.647), -$ (13:32:10.034), -{ (13:32:10.296), -age (13:32:11.143), -} (13:32:11.409), -years (13:32:12.609), -old (13:32:13.935), -` (13:32:14.220), -) (13:32:14.703), -; (13:32:15.376), -today (13:33:20.697) ~0.80, -break (13:38:13.369), -; (13:38:13.634), -break (13:38:15.507), -; (13:38:15.696), -break (13:38:17.679), -; (13:38:17.969), -break (13:38:20.154), -; (13:38:20.534), -break (13:38:22.736), -; (13:38:23.026), +todat (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -4752,11 +4752,11 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>90.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +browen (00:00:00), +charlie (00:00:00), +getday (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +today (00:00:00), +underfined (00:00:00), +view (00:00:00), -viewport (12:24:12.738), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
+          <t>+" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +Boolean (00:00:00), +Boolean (00:00:00), +browen (00:00:00), +charlie (00:00:00), +getday (00:00:00), +let (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +my (00:00:00), +myboolean (00:00:00), +myboolean (00:00:00), +myboolen (00:00:00), +myoolean (00:00:00), +number (00:00:00), +oppositeboolean (00:00:00), +port (00:00:00), +today (00:00:00), +underfined (00:00:00), +view (00:00:00), -viewport (12:24:12.738), -myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4769,11 +4769,11 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-myBoolean (12:36:27.967), -oppositeBoolean (12:36:43.817), -myBoolean (12:36:56.090), -myBoolean (12:38:28.108), -myBoolean (12:41:00.416), -myBoolean (12:41:10.665), -myBoolean (12:41:17.874), -! (12:43:12.831), -undefined (12:43:17.799), +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043), -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873), -Math (13:22:59.128), -Math (13:23:17.155), -Number (13:24:27.105), -; (13:26:07.158), -' (13:28:26.250), -! (13:28:30.583), -' (13:28:30.981), -; (13:28:31.528), -" (13:29:13.699), -\ (13:29:35.759), -\ (13:29:38.349), -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019), -getDay (13:35:54.315), -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +today (00:00:00), +getday (00:00:00)</t>
+          <t>-myBoolean (12:36:27.967) ~0.78, -oppositeBoolean (12:36:43.817) ~0.93, -myBoolean (12:36:56.090) ~0.89, -myBoolean (12:38:28.108), -myBoolean (12:41:00.416) ~0.89, -myBoolean (12:41:10.665) ~0.78, -myBoolean (12:41:17.874) ~0.89, -! (12:43:12.831), -undefined (12:43:17.799) ~0.90, +log* (12:53:22.757), -error (12:53:23.899), -; (13:02:35.373), -brown (13:05:24.043) ~0.83, -dog (13:07:08.730), -. (13:07:09.027), -name (13:07:10.103), -dog (13:07:35.114), -. (13:07:35.383), -name (13:07:36.414), -= (13:07:37.179), -" (13:07:37.700), -Charlie (13:07:39.223), -" (13:07:39.689), -; (13:07:39.891), -console (13:19:44.029), -. (13:19:44.184), -log (13:19:44.775), -( (13:19:45.020), -a (13:19:45.234), -+ (13:19:45.738), -b (13:19:46.169), -) (13:19:46.613), -; (13:19:50.458), -a (13:20:06.496), -= (13:20:07.087), -" (13:20:07.578), -5 (13:20:07.766), -" (13:20:08.157), -; (13:20:09.716), -Math (13:22:42.873) ~0.75, -Math (13:22:59.128) ~0.75, -Math (13:23:17.155) ~0.75, -Number (13:24:27.105) ~0.83, -' (13:28:26.250) ~0.00, -! (13:28:30.583), -' (13:28:30.981), -" (13:29:13.699), -\ (13:29:35.759) ~0.00, -\ (13:29:38.349) ~0.00, -let (13:33:19.021), -today (13:33:20.697), -= (13:33:22.176), -new (13:33:23.198), -Date (13:33:24.732), -( (13:33:24.813), -) (13:33:26.002), -; (13:33:26.327), -console (13:33:28.471), -. (13:33:28.731), -log (13:33:29.358), -( (13:33:29.664), -today (13:33:30.907), -) (13:33:31.316), -; (13:33:31.713), -someDate (13:33:51.019) ~0.25, -getDay (13:35:54.315) ~0.83, -default (13:37:00.967), -: (13:37:05.528), -console (13:37:07.678), -. (13:37:07.868), -log (13:37:08.517), -( (13:37:08.781), -" (13:37:09.037), -Weekend (13:37:10.693), -" (13:37:10.928), -) (13:37:11.144), -; (13:37:11.702), -break (13:38:10.544), -; (13:38:10.869), +let (00:00:00), +myboolen (00:00:00), +oppositeboolean (00:00:00), +myboolean (00:00:00), +my (00:00:00), +Boolean (00:00:00), +myoolean (00:00:00), +Boolean (00:00:00), +myboolean (00:00:00), +underfined (00:00:00), +browen (00:00:00), +charlie (00:00:00), +math (00:00:00), +math (00:00:00), +math (00:00:00), +number (00:00:00), +" (00:00:00), +/ (00:00:00), +/ (00:00:00), +; (00:00:00), +today (00:00:00), +getday (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -4875,11 +4875,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> , " (x2), ,, lig, oppositeBolean, log*</t>
+          <t xml:space="preserve"> , ,, lig, oppositeBolean, log*</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>+  (00:00:00), +" (00:00:00), +" (00:00:00), +, (00:00:00), +lig (00:00:00), +oppositeBolean (00:00:00), -log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969)</t>
+          <t>+  (00:00:00), +, (00:00:00), +lig (00:00:00), +oppositeBolean (00:00:00), -log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>+" (00:00:00), +" (00:00:00), +  (00:00:00)</t>
+          <t>+  (00:00:00)</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-log (12:35:41.570), -oppositeBoolean (12:36:43.817), +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969), +lig (00:00:00), +oppositeBolean (00:00:00), +, (00:00:00)</t>
+          <t>-log (12:35:41.570) ~0.67, -oppositeBoolean (12:36:43.817) ~0.93, +log* (12:53:22.757), -error (12:53:23.899), -; (13:38:17.969) ~0.00, +lig (00:00:00), +oppositeBolean (00:00:00), +, (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>-ol (12:30:53.144), +old (00:00:00)</t>
+          <t>-ol (12:30:53.144) ~0.67, +old (00:00:00)</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-% (13:22:03.842), +&amp; (00:00:00)</t>
+          <t>-% (13:22:03.842) ~0.00, +&amp; (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>+log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667), +somedate (00:00:00)</t>
+          <t>+log* (12:53:22.757), -error (12:53:23.899), -someDate (13:34:04.667) ~0.88, +somedate (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
